--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Aplicación/duoc/archivos de referencia/BBDD CLIENTES CM.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Aplicación/duoc/archivos de referencia/BBDD CLIENTES CM.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9900000051</t>
+          <t>5092891721</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -534,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32017771K</t>
+          <t>781467405</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9000002</t>
+          <t>1638676</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32017771K</t>
+          <t>781467405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9900000084</t>
+          <t>8593997503</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>320573662</t>
+          <t>784015270</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>320573662</t>
+          <t>784015270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9900000055</t>
+          <t>5716095802</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -699,12 +699,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>315822266</t>
+          <t>76464462K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9000040</t>
+          <t>9754807</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>315822266</t>
+          <t>76464462K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>56999000101</t>
+          <t>56938188002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9900000032</t>
+          <t>3738975628</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>317247684</t>
+          <t>770549221</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>317247684</t>
+          <t>770549221</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9900000017</t>
+          <t>2327139357</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>56999000102</t>
+          <t>56935304984</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>74207</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9900000074</t>
+          <t>7676307749</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -954,12 +954,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>320969617</t>
+          <t>784566781</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>900020</t>
+          <t>561284</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>320969617</t>
+          <t>784566781</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9900000091</t>
+          <t>9054925374</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56999000103</t>
+          <t>56949474410</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9900000041</t>
+          <t>4458192345</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31954419K</t>
+          <t>780098686</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31954419K</t>
+          <t>780098686</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>56999000104</t>
+          <t>56923088570</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9900000035</t>
+          <t>3879702798</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9000033</t>
+          <t>7312330</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9900000080</t>
+          <t>8304482332</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31693092K</t>
+          <t>769601902</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9000001</t>
+          <t>1286491</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31693092K</t>
+          <t>769601902</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>56999000105</t>
+          <t>56960305242</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9900000079</t>
+          <t>8294244131</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9900000001</t>
+          <t>1142203221</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>314792791</t>
+          <t>760389102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>314792791</t>
+          <t>760389102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>56999000106</t>
+          <t>56979990781</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1526,7 +1526,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9900000071</t>
+          <t>7380470856</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>316614161</t>
+          <t>768381798</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9000014</t>
+          <t>4094682</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1549,12 +1549,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>316614161</t>
+          <t>768381798</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>56999000107</t>
+          <t>56960046570</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9900000088</t>
+          <t>8865815672</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>315109551</t>
+          <t>761410121</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>315109551</t>
+          <t>761410121</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56999000108</t>
+          <t>56972312590</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9900000062</t>
+          <t>6406638629</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>320256904</t>
+          <t>781607932</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>320256904</t>
+          <t>781607932</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>56999000109</t>
+          <t>56918357654</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1776,7 +1776,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9900000072</t>
+          <t>7435668134</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>322315842</t>
+          <t>78720208K</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>322315842</t>
+          <t>78720208K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>56999000110</t>
+          <t>56918668598</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>90015</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9900000047</t>
+          <t>4936254645</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>318989866</t>
+          <t>778848988</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>318989866</t>
+          <t>778848988</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56999000111</t>
+          <t>56994841438</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9900000012</t>
+          <t>1853803852</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9000039</t>
+          <t>9689037</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9900000022</t>
+          <t>2534379800</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>322078279</t>
+          <t>786650968</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>322078279</t>
+          <t>786650968</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9900000049</t>
+          <t>5026590100</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31986095K</t>
+          <t>780635517</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31986095K</t>
+          <t>780635517</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2196,7 +2196,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9900000073</t>
+          <t>7462729157</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>321365568</t>
+          <t>785087658</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>321365568</t>
+          <t>785087658</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9900000070</t>
+          <t>7064661963</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9900000003</t>
+          <t>1315393763</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>315743071</t>
+          <t>764451589</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>315743071</t>
+          <t>764451589</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9900000078</t>
+          <t>8227547240</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>56999000112</t>
+          <t>56980052556</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9900000010</t>
+          <t>1733295235</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>320494476</t>
+          <t>783975408</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9000015</t>
+          <t>4667941</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>320494476</t>
+          <t>783975408</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>56999000113</t>
+          <t>56968379816</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9900000024</t>
+          <t>2713442447</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31803958K</t>
+          <t>774436960</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9000041</t>
+          <t>9925737</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31803958K</t>
+          <t>774436960</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9900000014</t>
+          <t>2057203373</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>316851735</t>
+          <t>768768595</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>900022</t>
+          <t>574488</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>316851735</t>
+          <t>768768595</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9900000099</t>
+          <t>9900519018</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>320415281</t>
+          <t>783782472</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>320415281</t>
+          <t>783782472</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9900000094</t>
+          <t>9482656350</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>315663883</t>
+          <t>76439173K</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>315663883</t>
+          <t>76439173K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2936,7 +2936,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9900000068</t>
+          <t>6960861787</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>316059836</t>
+          <t>766098681</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>316059836</t>
+          <t>766098681</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9900000077</t>
+          <t>8192379407</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>316139024</t>
+          <t>766591019</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9000036</t>
+          <t>8259097</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>316139024</t>
+          <t>766591019</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>56999000114</t>
+          <t>56978862799</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9900000066</t>
+          <t>6776693337</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>322236658</t>
+          <t>787162193</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9000028</t>
+          <t>6342646</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>322236658</t>
+          <t>787162193</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>56999000115</t>
+          <t>56949127700</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3191,7 +3191,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9900000011</t>
+          <t>1807217354</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>317960399</t>
+          <t>774214151</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>317960399</t>
+          <t>774214151</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9900000006</t>
+          <t>1596574008</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316693356</t>
+          <t>768382255</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9000007</t>
+          <t>2412179</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>316693356</t>
+          <t>768382255</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9900000086</t>
+          <t>8725101313</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>319781763</t>
+          <t>780621109</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9000031</t>
+          <t>6561882</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>319781763</t>
+          <t>780621109</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3441,7 +3441,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9900000093</t>
+          <t>9393490200</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>315584699</t>
+          <t>763731014</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9000005</t>
+          <t>2102683</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>315584699</t>
+          <t>763731014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>56999000116</t>
+          <t>56987182438</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3526,7 +3526,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9900000096</t>
+          <t>9535668073</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>322632604</t>
+          <t>789227977</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9000012</t>
+          <t>3858185</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>322632604</t>
+          <t>789227977</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>56999000117</t>
+          <t>56946292048</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3616,7 +3616,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9900000063</t>
+          <t>6457153541</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>318910673</t>
+          <t>778776715</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>318910673</t>
+          <t>778776715</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3696,7 +3696,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9900000030</t>
+          <t>3475811890</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>31788120K</t>
+          <t>774125817</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>31788120K</t>
+          <t>774125817</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9900000027</t>
+          <t>3024539566</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>316218219</t>
+          <t>76710166K</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>316218219</t>
+          <t>76710166K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9900000060</t>
+          <t>6305585035</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>321840709</t>
+          <t>786177855</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9000027</t>
+          <t>6154345</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>321840709</t>
+          <t>786177855</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>56999000118</t>
+          <t>56963404411</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3941,7 +3941,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9900000028</t>
+          <t>3194599248</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>321999086</t>
+          <t>786435366</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9000030</t>
+          <t>6557931</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>321999086</t>
+          <t>786435366</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>56999000119</t>
+          <t>56958967724</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4026,7 +4026,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9900000013</t>
+          <t>1991713125</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>320336097</t>
+          <t>782493094</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>900032</t>
+          <t>659040</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>320336097</t>
+          <t>782493094</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>65977</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9900000031</t>
+          <t>3650302361</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>318752294</t>
+          <t>777813455</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9000021</t>
+          <t>5627598</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>318752294</t>
+          <t>777813455</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>56999000120</t>
+          <t>56941991905</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>35335</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4206,7 +4206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9900000054</t>
+          <t>5667552469</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>318277157</t>
+          <t>775124903</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>318277157</t>
+          <t>775124903</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>85907</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4291,7 +4291,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9900000064</t>
+          <t>6651791797</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>314713602</t>
+          <t>760300896</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>314713602</t>
+          <t>760300896</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>56999000121</t>
+          <t>56996659440</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9900000038</t>
+          <t>4052190940</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>32081123K</t>
+          <t>784378403</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>32081123K</t>
+          <t>784378403</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>90022</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9900000026</t>
+          <t>3006170587</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>318831489</t>
+          <t>778721899</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9000037</t>
+          <t>8380945</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>318831489</t>
+          <t>778721899</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>56999000122</t>
+          <t>56940399197</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4541,7 +4541,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9900000037</t>
+          <t>3972490884</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>32255341K</t>
+          <t>789092117</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9000006</t>
+          <t>2385188</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>32255341K</t>
+          <t>789092117</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>56999000123</t>
+          <t>56923752183</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4631,7 +4631,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9900000042</t>
+          <t>4459177031</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>318197969</t>
+          <t>775045795</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>318197969</t>
+          <t>775045795</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4711,7 +4711,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9900000097</t>
+          <t>9749555232</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>319385812</t>
+          <t>779950506</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>580249</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>319385812</t>
+          <t>779950506</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>90017</t>
+          <t>51843</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4801,7 +4801,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9900000029</t>
+          <t>3195718600</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>321207187</t>
+          <t>784941485</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>321207187</t>
+          <t>784941485</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4881,7 +4881,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9900000069</t>
+          <t>6965739871</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>316455789</t>
+          <t>768018723</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>316455789</t>
+          <t>768018723</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4961,7 +4961,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9900000034</t>
+          <t>3858644576</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>319465000</t>
+          <t>779970299</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>319465000</t>
+          <t>779970299</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9900000100</t>
+          <t>9997175590</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>318593917</t>
+          <t>776544426</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9000034</t>
+          <t>8092583</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>318593917</t>
+          <t>776544426</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9900000056</t>
+          <t>5738364735</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>316297405</t>
+          <t>767569629</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>316297405</t>
+          <t>767569629</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5206,7 +5206,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9900000021</t>
+          <t>2508440552</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>319623384</t>
+          <t>780131993</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9000018</t>
+          <t>5513438</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>319623384</t>
+          <t>780131993</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9900000004</t>
+          <t>1365613775</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>315188746</t>
+          <t>761693050</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>315188746</t>
+          <t>761693050</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5376,7 +5376,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9900000076</t>
+          <t>8115241388</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>321127999</t>
+          <t>784893928</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>321127999</t>
+          <t>784893928</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9900000009</t>
+          <t>1690574962</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32168232K</t>
+          <t>785622774</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9000004</t>
+          <t>2013108</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>32168232K</t>
+          <t>785622774</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5541,7 +5541,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9900000052</t>
+          <t>5448735983</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>321603135</t>
+          <t>785394860</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9000008</t>
+          <t>2598591</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>321603135</t>
+          <t>785394860</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>56999000124</t>
+          <t>56923372910</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>57276</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5631,7 +5631,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9900000045</t>
+          <t>4763341403</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>315901450</t>
+          <t>764647661</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>315901450</t>
+          <t>764647661</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9900000057</t>
+          <t>5750804046</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>321286373</t>
+          <t>785074874</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9000010</t>
+          <t>3161562</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>321286373</t>
+          <t>785074874</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>56999000125</t>
+          <t>56969960163</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9900000044</t>
+          <t>4622164095</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>317326879</t>
+          <t>771056466</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9000025</t>
+          <t>5847592</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>317326879</t>
+          <t>771056466</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9900000016</t>
+          <t>2231648093</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>316534973</t>
+          <t>768235252</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>316534973</t>
+          <t>768235252</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5961,7 +5961,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9900000046</t>
+          <t>4919364601</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>315426313</t>
+          <t>763254283</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9000019</t>
+          <t>5554983</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>315426313</t>
+          <t>763254283</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9900000092</t>
+          <t>9269368597</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>315267930</t>
+          <t>761840673</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>315267930</t>
+          <t>761840673</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>56999000126</t>
+          <t>56919909650</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9900000053</t>
+          <t>5551923804</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>316772540</t>
+          <t>768610363</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9000013</t>
+          <t>4061433</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>316772540</t>
+          <t>768610363</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9900000048</t>
+          <t>4983292549</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>31716849K</t>
+          <t>770421705</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9000017</t>
+          <t>5337968</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>31716849K</t>
+          <t>770421705</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9900000098</t>
+          <t>9804519195</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>321919896</t>
+          <t>786282713</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>900009</t>
+          <t>271683</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>321919896</t>
+          <t>786282713</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6386,7 +6386,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9900000002</t>
+          <t>1205468262</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>314951176</t>
+          <t>760891053</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6404,12 +6404,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>314951176</t>
+          <t>760891053</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>56999000127</t>
+          <t>56967103861</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6466,7 +6466,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9900000081</t>
+          <t>8319517559</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>317485251</t>
+          <t>771370152</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>317485251</t>
+          <t>771370152</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>56999000128</t>
+          <t>56996387180</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6546,7 +6546,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9900000018</t>
+          <t>2411036485</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>320732045</t>
+          <t>784286177</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9000011</t>
+          <t>3210145</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>320732045</t>
+          <t>784286177</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6636,7 +6636,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9900000008</t>
+          <t>1656922637</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>319306628</t>
+          <t>779798534</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>319306628</t>
+          <t>779798534</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6721,7 +6721,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9900000058</t>
+          <t>5779141155</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>315980645</t>
+          <t>76495551K</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>315980645</t>
+          <t>76495551K</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>56999000129</t>
+          <t>56924351698</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6801,7 +6801,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9900000036</t>
+          <t>3912849287</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>316376594</t>
+          <t>767752067</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9000026</t>
+          <t>5942751</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>316376594</t>
+          <t>767752067</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9900000095</t>
+          <t>9488898894</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>315030369</t>
+          <t>761215922</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>315030369</t>
+          <t>761215922</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9900000033</t>
+          <t>3814692968</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>320652857</t>
+          <t>784282503</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>320652857</t>
+          <t>784282503</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9900000085</t>
+          <t>8663129710</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>320890424</t>
+          <t>784544184</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9000016</t>
+          <t>5041094</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>320890424</t>
+          <t>784544184</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>56999000130</t>
+          <t>56946774392</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7136,7 +7136,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9900000059</t>
+          <t>5839766943</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>318356341</t>
+          <t>77525887K</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9000029</t>
+          <t>6529960</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>318356341</t>
+          <t>77525887K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>56999000131</t>
+          <t>56929579020</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7226,7 +7226,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9900000050</t>
+          <t>5049975600</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>319940148</t>
+          <t>780915579</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>319940148</t>
+          <t>780915579</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>90020</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7311,7 +7311,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9900000083</t>
+          <t>8451634341</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>317564446</t>
+          <t>772691513</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9000038</t>
+          <t>9636528</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>317564446</t>
+          <t>772691513</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7396,7 +7396,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9900000082</t>
+          <t>8447291470</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>317406067</t>
+          <t>771232248</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>317406067</t>
+          <t>771232248</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>56999000132</t>
+          <t>56937702357</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7481,7 +7481,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9900000075</t>
+          <t>8001579214</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>318435538</t>
+          <t>77592392K</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>9000003</t>
+          <t>1760943</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>318435538</t>
+          <t>77592392K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9900000089</t>
+          <t>8870774999</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>319227433</t>
+          <t>779628256</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>319227433</t>
+          <t>779628256</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>56999000133</t>
+          <t>56983776752</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7651,7 +7651,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9900000020</t>
+          <t>2475002260</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>321761514</t>
+          <t>785918223</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>321761514</t>
+          <t>785918223</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>56999000134</t>
+          <t>56912300447</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7736,7 +7736,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9900000040</t>
+          <t>4173453615</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>322711795</t>
+          <t>789396787</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>322711795</t>
+          <t>789396787</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>56999000135</t>
+          <t>56930476546</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -7816,7 +7816,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9900000067</t>
+          <t>6872244916</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>317010118</t>
+          <t>769967885</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>317010118</t>
+          <t>769967885</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>56999000136</t>
+          <t>56998199120</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7901,7 +7901,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9900000019</t>
+          <t>2456730543</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>319148249</t>
+          <t>77932057K</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>319148249</t>
+          <t>77932057K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>90031</t>
+          <t>85273</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7986,7 +7986,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9900000005</t>
+          <t>1579225719</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>318673105</t>
+          <t>776645273</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>318673105</t>
+          <t>776645273</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8071,7 +8071,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9900000090</t>
+          <t>8975109690</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>322474225</t>
+          <t>788786115</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>322474225</t>
+          <t>788786115</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>56999000137</t>
+          <t>56991583008</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -8151,7 +8151,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9900000015</t>
+          <t>2128452457</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>319702579</t>
+          <t>780379014</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>319702579</t>
+          <t>780379014</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9900000039</t>
+          <t>4086206155</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>321523947</t>
+          <t>785367995</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9000024</t>
+          <t>5814024</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>321523947</t>
+          <t>785367995</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>56999000138</t>
+          <t>56919346137</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -8316,7 +8316,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9900000007</t>
+          <t>1606196082</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>318118774</t>
+          <t>774648844</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>318118774</t>
+          <t>774648844</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8401,7 +8401,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9900000025</t>
+          <t>2800621646</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>322157463</t>
+          <t>786882257</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>322157463</t>
+          <t>786882257</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>56999000139</t>
+          <t>56977403868</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>90006</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8486,7 +8486,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9900000043</t>
+          <t>4485001909</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>322395030</t>
+          <t>788239750</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>322395030</t>
+          <t>788239750</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9900000061</t>
+          <t>6360770924</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>317722827</t>
+          <t>77294845K</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>317722827</t>
+          <t>77294845K</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8651,7 +8651,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9900000023</t>
+          <t>2542007805</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>320098525</t>
+          <t>781445436</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8669,12 +8669,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>320098525</t>
+          <t>781445436</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>56999000140</t>
+          <t>56914104952</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9900000087</t>
+          <t>8790163358</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>314871988</t>
+          <t>76053577K</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>314871988</t>
+          <t>76053577K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>56999000141</t>
+          <t>56930846911</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>74272</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8816,7 +8816,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>9900000065</t>
+          <t>6690229987</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>315347129</t>
+          <t>76204756K</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9000035</t>
+          <t>8248480</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>315347129</t>
+          <t>76204756K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9900000051</t>
+          <t>5092891721</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32017771K</t>
+          <t>781467405</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9000002</t>
+          <t>1638676</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32017771K</t>
+          <t>781467405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -9102,7 +9102,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9900000084</t>
+          <t>8593997503</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>320573662</t>
+          <t>784015270</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>320573662</t>
+          <t>784015270</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -9182,7 +9182,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9900000055</t>
+          <t>5716095802</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>315822266</t>
+          <t>76464462K</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9000040</t>
+          <t>9754807</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>315822266</t>
+          <t>76464462K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>56999000101</t>
+          <t>56938188002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9900000032</t>
+          <t>3738975628</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>317247684</t>
+          <t>770549221</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>317247684</t>
+          <t>770549221</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9352,7 +9352,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9900000017</t>
+          <t>2327139357</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>319069052</t>
+          <t>77918675K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>56999000102</t>
+          <t>56935304984</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90026</t>
+          <t>74207</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -9437,7 +9437,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9900000074</t>
+          <t>7676307749</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>320969617</t>
+          <t>784566781</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>900020</t>
+          <t>561284</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>320969617</t>
+          <t>784566781</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -9522,7 +9522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9900000091</t>
+          <t>9054925374</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>321444752</t>
+          <t>785172752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56999000103</t>
+          <t>56949474410</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -9602,7 +9602,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9900000041</t>
+          <t>4458192345</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>31954419K</t>
+          <t>780098686</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31954419K</t>
+          <t>780098686</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>56999000104</t>
+          <t>56923088570</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9682,7 +9682,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9900000035</t>
+          <t>3879702798</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9000033</t>
+          <t>7312330</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32279098K</t>
+          <t>789555699</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9767,7 +9767,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9900000080</t>
+          <t>8304482332</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31693092K</t>
+          <t>769601902</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9000001</t>
+          <t>1286491</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31693092K</t>
+          <t>769601902</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>56999000105</t>
+          <t>56960305242</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -9852,7 +9852,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9900000079</t>
+          <t>8294244131</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>317643630</t>
+          <t>772902824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -9932,7 +9932,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9900000001</t>
+          <t>1142203221</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>314792791</t>
+          <t>760389102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>314792791</t>
+          <t>760389102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>56999000106</t>
+          <t>56979990781</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -10017,7 +10017,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9900000071</t>
+          <t>7380470856</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>316614161</t>
+          <t>768381798</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9000014</t>
+          <t>4094682</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10040,12 +10040,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>316614161</t>
+          <t>768381798</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>56999000107</t>
+          <t>56960046570</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -10107,7 +10107,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9900000088</t>
+          <t>8865815672</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>315109551</t>
+          <t>761410121</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>315109551</t>
+          <t>761410121</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56999000108</t>
+          <t>56972312590</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -10187,7 +10187,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9900000062</t>
+          <t>6406638629</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>320256904</t>
+          <t>781607932</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>320256904</t>
+          <t>781607932</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>56999000109</t>
+          <t>56918357654</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -10267,7 +10267,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9900000072</t>
+          <t>7435668134</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>322315842</t>
+          <t>78720208K</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>322315842</t>
+          <t>78720208K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>56999000110</t>
+          <t>56918668598</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>90015</t>
+          <t>46605</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -10352,7 +10352,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9900000047</t>
+          <t>4936254645</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>318989866</t>
+          <t>778848988</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>318989866</t>
+          <t>778848988</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56999000111</t>
+          <t>56994841438</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10432,7 +10432,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9900000012</t>
+          <t>1853803852</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9000039</t>
+          <t>9689037</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>315505508</t>
+          <t>763484025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9900000022</t>
+          <t>2534379800</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>322078279</t>
+          <t>786650968</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>322078279</t>
+          <t>786650968</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -10602,7 +10602,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9900000049</t>
+          <t>5026590100</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31986095K</t>
+          <t>780635517</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31986095K</t>
+          <t>780635517</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10687,7 +10687,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9900000073</t>
+          <t>7462729157</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>321365568</t>
+          <t>785087658</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>321365568</t>
+          <t>785087658</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9900000070</t>
+          <t>7064661963</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>32104880K</t>
+          <t>784579840</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10852,7 +10852,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9900000003</t>
+          <t>1315393763</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>315743071</t>
+          <t>764451589</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>315743071</t>
+          <t>764451589</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10932,7 +10932,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9900000078</t>
+          <t>8227547240</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10950,12 +10950,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>317802015</t>
+          <t>773747253</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>56999000112</t>
+          <t>56980052556</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -11012,7 +11012,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9900000010</t>
+          <t>1733295235</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>320494476</t>
+          <t>783975408</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9000015</t>
+          <t>4667941</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>320494476</t>
+          <t>783975408</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>56999000113</t>
+          <t>56968379816</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11097,7 +11097,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9900000024</t>
+          <t>2713442447</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31803958K</t>
+          <t>774436960</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9000041</t>
+          <t>9925737</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31803958K</t>
+          <t>774436960</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11182,7 +11182,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9900000014</t>
+          <t>2057203373</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>316851735</t>
+          <t>768768595</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>900022</t>
+          <t>574488</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>316851735</t>
+          <t>768768595</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11267,7 +11267,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9900000099</t>
+          <t>9900519018</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>320415281</t>
+          <t>783782472</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>320415281</t>
+          <t>783782472</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -11347,7 +11347,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9900000094</t>
+          <t>9482656350</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>315663883</t>
+          <t>76439173K</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>315663883</t>
+          <t>76439173K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -11427,7 +11427,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9900000068</t>
+          <t>6960861787</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>316059836</t>
+          <t>766098681</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>316059836</t>
+          <t>766098681</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -11512,7 +11512,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9900000077</t>
+          <t>8192379407</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>316139024</t>
+          <t>766591019</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9000036</t>
+          <t>8259097</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>316139024</t>
+          <t>766591019</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>56999000114</t>
+          <t>56978862799</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -11597,7 +11597,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9900000066</t>
+          <t>6776693337</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>322236658</t>
+          <t>787162193</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9000028</t>
+          <t>6342646</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>322236658</t>
+          <t>787162193</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>56999000115</t>
+          <t>56949127700</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -11682,7 +11682,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9900000011</t>
+          <t>1807217354</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>317960399</t>
+          <t>774214151</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>317960399</t>
+          <t>774214151</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -11762,7 +11762,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9900000006</t>
+          <t>1596574008</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -11770,12 +11770,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>316693356</t>
+          <t>768382255</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9000007</t>
+          <t>2412179</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>316693356</t>
+          <t>768382255</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -11847,7 +11847,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9900000086</t>
+          <t>8725101313</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>319781763</t>
+          <t>780621109</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9000031</t>
+          <t>6561882</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>319781763</t>
+          <t>780621109</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -11932,7 +11932,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9900000093</t>
+          <t>9393490200</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>315584699</t>
+          <t>763731014</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9000005</t>
+          <t>2102683</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>315584699</t>
+          <t>763731014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>56999000116</t>
+          <t>56987182438</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -12017,7 +12017,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9900000096</t>
+          <t>9535668073</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>322632604</t>
+          <t>789227977</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9000012</t>
+          <t>3858185</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>322632604</t>
+          <t>789227977</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>56999000117</t>
+          <t>56946292048</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>72250</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -12107,7 +12107,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9900000063</t>
+          <t>6457153541</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>318910673</t>
+          <t>778776715</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>318910673</t>
+          <t>778776715</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9900000030</t>
+          <t>3475811890</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>31788120K</t>
+          <t>774125817</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>31788120K</t>
+          <t>774125817</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9900000027</t>
+          <t>3024539566</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>316218219</t>
+          <t>76710166K</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>316218219</t>
+          <t>76710166K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -12347,7 +12347,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9900000060</t>
+          <t>6305585035</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>321840709</t>
+          <t>786177855</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9000027</t>
+          <t>6154345</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>321840709</t>
+          <t>786177855</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>56999000118</t>
+          <t>56963404411</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -12432,7 +12432,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9900000028</t>
+          <t>3194599248</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>321999086</t>
+          <t>786435366</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9000030</t>
+          <t>6557931</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>321999086</t>
+          <t>786435366</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>56999000119</t>
+          <t>56958967724</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9900000013</t>
+          <t>1991713125</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>320336097</t>
+          <t>782493094</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>900032</t>
+          <t>659040</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>320336097</t>
+          <t>782493094</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>65977</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -12607,7 +12607,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9900000031</t>
+          <t>3650302361</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>318752294</t>
+          <t>777813455</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9000021</t>
+          <t>5627598</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>318752294</t>
+          <t>777813455</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>56999000120</t>
+          <t>56941991905</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>35335</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -12697,7 +12697,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9900000054</t>
+          <t>5667552469</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>318277157</t>
+          <t>775124903</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>318277157</t>
+          <t>775124903</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>90032</t>
+          <t>85907</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -12782,7 +12782,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9900000064</t>
+          <t>6651791797</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>314713602</t>
+          <t>760300896</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>314713602</t>
+          <t>760300896</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>56999000121</t>
+          <t>56996659440</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -12862,7 +12862,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9900000038</t>
+          <t>4052190940</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>32081123K</t>
+          <t>784378403</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>32081123K</t>
+          <t>784378403</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>90022</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9900000026</t>
+          <t>3006170587</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>318831489</t>
+          <t>778721899</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9000037</t>
+          <t>8380945</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>318831489</t>
+          <t>778721899</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>56999000122</t>
+          <t>56940399197</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13032,7 +13032,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9900000037</t>
+          <t>3972490884</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>32255341K</t>
+          <t>789092117</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9000006</t>
+          <t>2385188</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>32255341K</t>
+          <t>789092117</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>56999000123</t>
+          <t>56923752183</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -13085,7 +13085,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -13122,7 +13122,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9900000042</t>
+          <t>4459177031</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>318197969</t>
+          <t>775045795</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>318197969</t>
+          <t>775045795</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9900000097</t>
+          <t>9749555232</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -13210,12 +13210,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>319385812</t>
+          <t>779950506</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>580249</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>319385812</t>
+          <t>779950506</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>90017</t>
+          <t>51843</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -13292,7 +13292,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9900000029</t>
+          <t>3195718600</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>321207187</t>
+          <t>784941485</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>321207187</t>
+          <t>784941485</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -13372,7 +13372,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9900000069</t>
+          <t>6965739871</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>316455789</t>
+          <t>768018723</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>316455789</t>
+          <t>768018723</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -13452,7 +13452,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9900000034</t>
+          <t>3858644576</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>319465000</t>
+          <t>779970299</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>319465000</t>
+          <t>779970299</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -13532,7 +13532,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9900000100</t>
+          <t>9997175590</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -13540,12 +13540,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>318593917</t>
+          <t>776544426</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9000034</t>
+          <t>8092583</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>318593917</t>
+          <t>776544426</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -13617,7 +13617,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9900000056</t>
+          <t>5738364735</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>316297405</t>
+          <t>767569629</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>316297405</t>
+          <t>767569629</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -13697,7 +13697,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9900000021</t>
+          <t>2508440552</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>319623384</t>
+          <t>780131993</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9000018</t>
+          <t>5513438</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>319623384</t>
+          <t>780131993</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -13782,7 +13782,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9900000004</t>
+          <t>1365613775</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>315188746</t>
+          <t>761693050</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>315188746</t>
+          <t>761693050</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -13867,7 +13867,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9900000076</t>
+          <t>8115241388</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>321127999</t>
+          <t>784893928</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>321127999</t>
+          <t>784893928</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -13947,7 +13947,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9900000009</t>
+          <t>1690574962</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32168232K</t>
+          <t>785622774</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9000004</t>
+          <t>2013108</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>32168232K</t>
+          <t>785622774</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -14032,7 +14032,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9900000052</t>
+          <t>5448735983</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -14040,12 +14040,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>321603135</t>
+          <t>785394860</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9000008</t>
+          <t>2598591</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -14055,12 +14055,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>321603135</t>
+          <t>785394860</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>56999000124</t>
+          <t>56923372910</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>57276</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -14122,7 +14122,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9900000045</t>
+          <t>4763341403</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>315901450</t>
+          <t>764647661</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>315901450</t>
+          <t>764647661</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -14202,7 +14202,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9900000057</t>
+          <t>5750804046</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -14210,12 +14210,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>321286373</t>
+          <t>785074874</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9000010</t>
+          <t>3161562</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>321286373</t>
+          <t>785074874</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>56999000125</t>
+          <t>56969960163</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -14287,7 +14287,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9900000044</t>
+          <t>4622164095</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>317326879</t>
+          <t>771056466</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9000025</t>
+          <t>5847592</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>317326879</t>
+          <t>771056466</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -14372,7 +14372,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9900000016</t>
+          <t>2231648093</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>316534973</t>
+          <t>768235252</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>316534973</t>
+          <t>768235252</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -14452,7 +14452,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9900000046</t>
+          <t>4919364601</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>315426313</t>
+          <t>763254283</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9000019</t>
+          <t>5554983</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>315426313</t>
+          <t>763254283</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -14537,7 +14537,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9900000092</t>
+          <t>9269368597</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>315267930</t>
+          <t>761840673</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -14555,12 +14555,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>315267930</t>
+          <t>761840673</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>56999000126</t>
+          <t>56919909650</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -14617,7 +14617,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9900000053</t>
+          <t>5551923804</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>316772540</t>
+          <t>768610363</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9000013</t>
+          <t>4061433</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>316772540</t>
+          <t>768610363</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -14707,7 +14707,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9900000048</t>
+          <t>4983292549</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>31716849K</t>
+          <t>770421705</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9000017</t>
+          <t>5337968</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>31716849K</t>
+          <t>770421705</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -14792,7 +14792,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9900000098</t>
+          <t>9804519195</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -14800,12 +14800,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>321919896</t>
+          <t>786282713</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>900009</t>
+          <t>271683</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>321919896</t>
+          <t>786282713</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -14877,7 +14877,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9900000002</t>
+          <t>1205468262</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>314951176</t>
+          <t>760891053</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>314951176</t>
+          <t>760891053</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>56999000127</t>
+          <t>56967103861</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -14957,7 +14957,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9900000081</t>
+          <t>8319517559</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>317485251</t>
+          <t>771370152</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>317485251</t>
+          <t>771370152</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>56999000128</t>
+          <t>56996387180</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -15037,7 +15037,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9900000018</t>
+          <t>2411036485</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>320732045</t>
+          <t>784286177</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9000011</t>
+          <t>3210145</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>320732045</t>
+          <t>784286177</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -15127,7 +15127,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9900000008</t>
+          <t>1656922637</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>319306628</t>
+          <t>779798534</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>319306628</t>
+          <t>779798534</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -15212,7 +15212,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9900000058</t>
+          <t>5779141155</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>315980645</t>
+          <t>76495551K</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>315980645</t>
+          <t>76495551K</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>56999000129</t>
+          <t>56924351698</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -15292,7 +15292,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9900000036</t>
+          <t>3912849287</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>316376594</t>
+          <t>767752067</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9000026</t>
+          <t>5942751</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>316376594</t>
+          <t>767752067</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -15377,7 +15377,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9900000095</t>
+          <t>9488898894</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>315030369</t>
+          <t>761215922</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>315030369</t>
+          <t>761215922</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -15457,7 +15457,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9900000033</t>
+          <t>3814692968</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>320652857</t>
+          <t>784282503</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>320652857</t>
+          <t>784282503</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -15537,7 +15537,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9900000085</t>
+          <t>8663129710</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>320890424</t>
+          <t>784544184</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9000016</t>
+          <t>5041094</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>320890424</t>
+          <t>784544184</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>56999000130</t>
+          <t>56946774392</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -15627,7 +15627,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9900000059</t>
+          <t>5839766943</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15635,12 +15635,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>318356341</t>
+          <t>77525887K</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9000029</t>
+          <t>6529960</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -15650,12 +15650,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>318356341</t>
+          <t>77525887K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>56999000131</t>
+          <t>56929579020</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -15717,7 +15717,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9900000050</t>
+          <t>5049975600</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>319940148</t>
+          <t>780915579</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>319940148</t>
+          <t>780915579</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -15755,7 +15755,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>90020</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15802,7 +15802,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9900000083</t>
+          <t>8451634341</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15810,12 +15810,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>317564446</t>
+          <t>772691513</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9000038</t>
+          <t>9636528</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>317564446</t>
+          <t>772691513</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -15887,7 +15887,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9900000082</t>
+          <t>8447291470</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>317406067</t>
+          <t>771232248</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -15905,12 +15905,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>317406067</t>
+          <t>771232248</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>56999000132</t>
+          <t>56937702357</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -15972,7 +15972,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9900000075</t>
+          <t>8001579214</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>318435538</t>
+          <t>77592392K</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>9000003</t>
+          <t>1760943</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>318435538</t>
+          <t>77592392K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -16057,7 +16057,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9900000089</t>
+          <t>8870774999</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -16065,7 +16065,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>319227433</t>
+          <t>779628256</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -16075,12 +16075,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>319227433</t>
+          <t>779628256</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>56999000133</t>
+          <t>56983776752</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -16142,7 +16142,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9900000020</t>
+          <t>2475002260</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>321761514</t>
+          <t>785918223</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -16160,12 +16160,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>321761514</t>
+          <t>785918223</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>56999000134</t>
+          <t>56912300447</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>90034</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -16227,7 +16227,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9900000040</t>
+          <t>4173453615</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>322711795</t>
+          <t>789396787</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -16245,12 +16245,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>322711795</t>
+          <t>789396787</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>56999000135</t>
+          <t>56930476546</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -16307,7 +16307,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9900000067</t>
+          <t>6872244916</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -16315,7 +16315,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>317010118</t>
+          <t>769967885</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -16325,12 +16325,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>317010118</t>
+          <t>769967885</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>56999000136</t>
+          <t>56998199120</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16345,7 +16345,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -16392,7 +16392,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9900000019</t>
+          <t>2456730543</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>319148249</t>
+          <t>77932057K</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>319148249</t>
+          <t>77932057K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>90031</t>
+          <t>85273</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16477,7 +16477,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9900000005</t>
+          <t>1579225719</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>318673105</t>
+          <t>776645273</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -16495,7 +16495,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>318673105</t>
+          <t>776645273</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -16515,7 +16515,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -16562,7 +16562,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9900000090</t>
+          <t>8975109690</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>322474225</t>
+          <t>788786115</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -16580,12 +16580,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>322474225</t>
+          <t>788786115</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>56999000137</t>
+          <t>56991583008</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -16642,7 +16642,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9900000015</t>
+          <t>2128452457</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>319702579</t>
+          <t>780379014</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>319702579</t>
+          <t>780379014</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -16722,7 +16722,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9900000039</t>
+          <t>4086206155</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>321523947</t>
+          <t>785367995</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9000024</t>
+          <t>5814024</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>321523947</t>
+          <t>785367995</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>56999000138</t>
+          <t>56919346137</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -16807,7 +16807,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9900000007</t>
+          <t>1606196082</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>318118774</t>
+          <t>774648844</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>318118774</t>
+          <t>774648844</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -16892,7 +16892,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9900000025</t>
+          <t>2800621646</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>322157463</t>
+          <t>786882257</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -16910,12 +16910,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>322157463</t>
+          <t>786882257</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>56999000139</t>
+          <t>56977403868</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>90006</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -16977,7 +16977,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9900000043</t>
+          <t>4485001909</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>322395030</t>
+          <t>788239750</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>322395030</t>
+          <t>788239750</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -17057,7 +17057,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9900000061</t>
+          <t>6360770924</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>317722827</t>
+          <t>77294845K</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>317722827</t>
+          <t>77294845K</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17142,7 +17142,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9900000023</t>
+          <t>2542007805</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>320098525</t>
+          <t>781445436</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>320098525</t>
+          <t>781445436</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>56999000140</t>
+          <t>56914104952</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -17222,7 +17222,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9900000087</t>
+          <t>8790163358</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>314871988</t>
+          <t>76053577K</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -17240,12 +17240,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>314871988</t>
+          <t>76053577K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>56999000141</t>
+          <t>56930846911</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>74272</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -17307,7 +17307,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>9900000065</t>
+          <t>6690229987</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -17315,12 +17315,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>315347129</t>
+          <t>76204756K</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9000035</t>
+          <t>8248480</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>315347129</t>
+          <t>76204756K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -17350,7 +17350,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Nueva Venta  de Camiones Empresa Demo</t>
+          <t>Nueva Venta  de Camiones Volvo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
